--- a/consent_forms/006_escape_room_consent_form--consent_forms.xlsx
+++ b/consent_forms/006_escape_room_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1351,36 +1351,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>i_will_not_touch_any_objects_or_devices_that_are_not_allowed</t>
+          <t>i_will_not_push_or_pull_any_objects_that_are_not_allowed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>I will not touch any objects or devices that are not allowed</t>
+          <t>I will not push or pull any objects that are not allowed</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>student_agreement_choices</t>
+          <t>emergency_contact_agreement_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>i_will_not_push_or_pull_any_objects_that_are_not_allowed</t>
+          <t>i_will_not_touch_any_objects_or_devices_that_are_not_allowed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>I will not push or pull any objects that are not allowed</t>
+          <t>I will not touch any objects or devices that are not allowed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>student_agreement_choices</t>
+          <t>emergency_contact_agreement_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1397,68 +1397,68 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>emergency_contact_agreement_choices</t>
+          <t>school_grade_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>i_will_not_touch_any_objects_or_devices_that_are_not_allowed</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>I will not touch any objects or devices that are not allowed</t>
+          <t>1st</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_contact_agreement_choices</t>
+          <t>school_grade_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>i_will_not_touch_any_objects_or_devices_that_are_not_allowed</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>I will not touch any objects or devices that are not allowed</t>
+          <t>2nd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>emergency_contact_agreement_choices</t>
+          <t>school_grade_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>i_will_not_push_or_pull_any_objects_that_are_not_allowed</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>I will not push or pull any objects that are not allowed</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>emergency_contact_agreement_choices</t>
+          <t>school_grade_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>i_will_not_push_or_pull_any_objects_that_are_not_allowed</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>I will not push or pull any objects that are not allowed</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>5th</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>6th</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>7th</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>7th</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>8th</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>8th</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>9th</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>9th</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>10th</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>11th</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>11th</t>
         </is>
       </c>
     </row>
@@ -1589,214 +1589,146 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8th</t>
+          <t>12th</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>8th</t>
+          <t>12th</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>school_grade_choices</t>
+          <t>event_time_duration_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>school_grade_choices</t>
+          <t>event_time_duration_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>school_grade_choices</t>
+          <t>event_location_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11th</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11th</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>school_grade_choices</t>
+          <t>event_location_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12th</t>
+          <t>off-site</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12th</t>
+          <t>Off-site</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>event_time_duration_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>escape_room_challenge_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Escape Room Challenge 1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>event_time_duration_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>escape_room_challenge_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>Escape Room Challenge 2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>event_location_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>on-site</t>
+          <t>team_challenge_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Team Challenge 1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>event_location_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>off-site</t>
+          <t>team_challenge_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
-        <is>
-          <t>Off-site</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>event_type_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>escape_room_challenge_1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Escape Room Challenge 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>event_type_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>escape_room_challenge_2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Escape Room Challenge 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>event_type_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>team_challenge_1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Team Challenge 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>event_type_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>team_challenge_2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
         <is>
           <t>Team Challenge 2</t>
         </is>
